--- a/data/odds/2026 Family League 2026 Betting Odds.xlsx
+++ b/data/odds/2026 Family League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="62">
   <si>
     <t>Record</t>
   </si>
@@ -36,6 +36,9 @@
     <t>For Me to Poop On</t>
   </si>
   <si>
+    <t>Your Mom</t>
+  </si>
+  <si>
     <t>That movie was great...</t>
   </si>
   <si>
@@ -45,145 +48,160 @@
     <t>Delco Dee</t>
   </si>
   <si>
+    <t>lawrence's Lucrative Team</t>
+  </si>
+  <si>
     <t>Big Bosh Bashers</t>
   </si>
   <si>
-    <t>Your Mom</t>
-  </si>
-  <si>
     <t>Jackson's Scary Team</t>
   </si>
   <si>
-    <t>lawrence's Lucrative Team</t>
-  </si>
-  <si>
-    <t>Michael's Magnificent Team</t>
+    <t>Ragebaiters</t>
+  </si>
+  <si>
+    <t>Flacillionares</t>
   </si>
   <si>
     <t>ICSquirrels</t>
   </si>
   <si>
-    <t>Flacillionares</t>
-  </si>
-  <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>1-1</t>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>1-2</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>75.1%</t>
-  </si>
-  <si>
-    <t>74.2%</t>
-  </si>
-  <si>
-    <t>69.0%</t>
-  </si>
-  <si>
-    <t>64.1%</t>
-  </si>
-  <si>
-    <t>50.2%</t>
-  </si>
-  <si>
-    <t>42.0%</t>
-  </si>
-  <si>
-    <t>13.9%</t>
-  </si>
-  <si>
-    <t>11.5%</t>
+    <t>92.2%</t>
+  </si>
+  <si>
+    <t>88.5%</t>
+  </si>
+  <si>
+    <t>84.1%</t>
+  </si>
+  <si>
+    <t>48.3%</t>
+  </si>
+  <si>
+    <t>42.1%</t>
+  </si>
+  <si>
+    <t>22.4%</t>
+  </si>
+  <si>
+    <t>15.5%</t>
+  </si>
+  <si>
+    <t>6.6%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-1182</t>
+  </si>
+  <si>
+    <t>-770</t>
+  </si>
+  <si>
+    <t>-529</t>
+  </si>
+  <si>
+    <t>+107</t>
+  </si>
+  <si>
+    <t>+138</t>
+  </si>
+  <si>
+    <t>+346</t>
+  </si>
+  <si>
+    <t>+545</t>
+  </si>
+  <si>
+    <t>+1415</t>
+  </si>
+  <si>
+    <t>+49900</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>77.2%</t>
+  </si>
+  <si>
+    <t>22.0%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-∞</t>
-  </si>
-  <si>
-    <t>-302</t>
-  </si>
-  <si>
-    <t>-288</t>
-  </si>
-  <si>
-    <t>-223</t>
-  </si>
-  <si>
-    <t>-179</t>
-  </si>
-  <si>
-    <t>-101</t>
-  </si>
-  <si>
-    <t>+138</t>
-  </si>
-  <si>
-    <t>+619</t>
-  </si>
-  <si>
-    <t>+770</t>
-  </si>
-  <si>
-    <t>+∞</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>76.5%</t>
-  </si>
-  <si>
-    <t>21.2%</t>
-  </si>
-  <si>
-    <t>1.4%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>-326</t>
-  </si>
-  <si>
-    <t>+372</t>
-  </si>
-  <si>
-    <t>+7043</t>
-  </si>
-  <si>
-    <t>+16567</t>
+    <t>-339</t>
+  </si>
+  <si>
+    <t>+355</t>
+  </si>
+  <si>
+    <t>+19900</t>
   </si>
   <si>
     <t>+33233</t>
   </si>
   <si>
-    <t>52.9%</t>
-  </si>
-  <si>
-    <t>46.9%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>-112</t>
-  </si>
-  <si>
-    <t>+113</t>
-  </si>
-  <si>
-    <t>+99900</t>
+    <t>68.5%</t>
+  </si>
+  <si>
+    <t>26.2%</t>
+  </si>
+  <si>
+    <t>2.6%</t>
+  </si>
+  <si>
+    <t>1.8%</t>
+  </si>
+  <si>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>-217</t>
+  </si>
+  <si>
+    <t>+282</t>
+  </si>
+  <si>
+    <t>+3746</t>
+  </si>
+  <si>
+    <t>+5456</t>
+  </si>
+  <si>
+    <t>+14186</t>
   </si>
 </sst>
 </file>
@@ -566,10 +584,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -580,10 +598,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -591,13 +609,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -608,10 +626,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -619,13 +637,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -636,10 +654,10 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -647,13 +665,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -661,13 +679,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -675,13 +693,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -689,13 +707,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -703,13 +721,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -717,13 +735,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -744,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -752,30 +770,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -783,139 +801,139 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -936,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -947,13 +965,13 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -961,13 +979,13 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -975,139 +993,139 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/2026 Family League 2026 Betting Odds.xlsx
+++ b/data/odds/2026 Family League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="67">
   <si>
     <t>Record</t>
   </si>
@@ -36,172 +36,187 @@
     <t>For Me to Poop On</t>
   </si>
   <si>
+    <t>Gabe's Great Team</t>
+  </si>
+  <si>
+    <t>That movie was great...</t>
+  </si>
+  <si>
     <t>Your Mom</t>
   </si>
   <si>
-    <t>That movie was great...</t>
-  </si>
-  <si>
-    <t>Gabe's Great Team</t>
+    <t>Jackson's Scary Team</t>
+  </si>
+  <si>
+    <t>Ragebaiters</t>
+  </si>
+  <si>
+    <t>Big Bosh Bashers</t>
+  </si>
+  <si>
+    <t>lawrence's Lucrative Team</t>
   </si>
   <si>
     <t>Delco Dee</t>
   </si>
   <si>
-    <t>lawrence's Lucrative Team</t>
-  </si>
-  <si>
-    <t>Big Bosh Bashers</t>
-  </si>
-  <si>
-    <t>Jackson's Scary Team</t>
-  </si>
-  <si>
-    <t>Ragebaiters</t>
+    <t>ICSquirrels</t>
   </si>
   <si>
     <t>Flacillionares</t>
   </si>
   <si>
-    <t>ICSquirrels</t>
-  </si>
-  <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>0-3</t>
-  </si>
-  <si>
-    <t>1-2</t>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>1-3</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>92.2%</t>
-  </si>
-  <si>
-    <t>88.5%</t>
-  </si>
-  <si>
-    <t>84.1%</t>
-  </si>
-  <si>
-    <t>48.3%</t>
-  </si>
-  <si>
-    <t>42.1%</t>
-  </si>
-  <si>
-    <t>22.4%</t>
-  </si>
-  <si>
-    <t>15.5%</t>
-  </si>
-  <si>
-    <t>6.6%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
+    <t>97.9%</t>
+  </si>
+  <si>
+    <t>94.3%</t>
+  </si>
+  <si>
+    <t>73.3%</t>
+  </si>
+  <si>
+    <t>67.1%</t>
+  </si>
+  <si>
+    <t>25.1%</t>
+  </si>
+  <si>
+    <t>22.3%</t>
+  </si>
+  <si>
+    <t>13.3%</t>
+  </si>
+  <si>
+    <t>5.0%</t>
+  </si>
+  <si>
+    <t>1.7%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-4662</t>
+  </si>
+  <si>
+    <t>-1654</t>
+  </si>
+  <si>
+    <t>-275</t>
+  </si>
+  <si>
+    <t>-204</t>
+  </si>
+  <si>
+    <t>+298</t>
+  </si>
+  <si>
+    <t>+348</t>
+  </si>
+  <si>
+    <t>+652</t>
+  </si>
+  <si>
+    <t>+1900</t>
+  </si>
+  <si>
+    <t>+5782</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>49.4%</t>
+  </si>
+  <si>
+    <t>40.0%</t>
+  </si>
+  <si>
+    <t>6.4%</t>
+  </si>
+  <si>
+    <t>3.6%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
   </si>
   <si>
     <t>0.1%</t>
   </si>
   <si>
-    <t>-99900</t>
-  </si>
-  <si>
-    <t>-1182</t>
-  </si>
-  <si>
-    <t>-770</t>
-  </si>
-  <si>
-    <t>-529</t>
-  </si>
-  <si>
-    <t>+107</t>
-  </si>
-  <si>
-    <t>+138</t>
-  </si>
-  <si>
-    <t>+346</t>
-  </si>
-  <si>
-    <t>+545</t>
-  </si>
-  <si>
-    <t>+1415</t>
-  </si>
-  <si>
-    <t>+49900</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>77.2%</t>
-  </si>
-  <si>
-    <t>22.0%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-339</t>
-  </si>
-  <si>
-    <t>+355</t>
+    <t>+102</t>
+  </si>
+  <si>
+    <t>+150</t>
+  </si>
+  <si>
+    <t>+1462</t>
+  </si>
+  <si>
+    <t>+2678</t>
   </si>
   <si>
     <t>+19900</t>
   </si>
   <si>
-    <t>+33233</t>
-  </si>
-  <si>
     <t>68.5%</t>
   </si>
   <si>
-    <t>26.2%</t>
-  </si>
-  <si>
-    <t>2.6%</t>
+    <t>19.9%</t>
+  </si>
+  <si>
+    <t>6.8%</t>
   </si>
   <si>
     <t>1.8%</t>
   </si>
   <si>
-    <t>0.7%</t>
+    <t>1.5%</t>
+  </si>
+  <si>
+    <t>1.4%</t>
   </si>
   <si>
     <t>-217</t>
   </si>
   <si>
-    <t>+282</t>
-  </si>
-  <si>
-    <t>+3746</t>
+    <t>+403</t>
+  </si>
+  <si>
+    <t>+1371</t>
   </si>
   <si>
     <t>+5456</t>
   </si>
   <si>
-    <t>+14186</t>
+    <t>+6567</t>
+  </si>
+  <si>
+    <t>+7043</t>
   </si>
 </sst>
 </file>
@@ -584,10 +599,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -595,13 +610,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -609,13 +624,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -626,10 +641,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -637,13 +652,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -654,10 +669,10 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -665,13 +680,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -679,13 +694,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -693,13 +708,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -707,13 +722,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -721,13 +736,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -735,13 +750,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -762,7 +777,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -770,30 +785,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -801,13 +816,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -818,122 +833,122 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -954,7 +969,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -965,13 +980,13 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -979,13 +994,13 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -993,69 +1008,69 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1066,24 +1081,24 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1091,27 +1106,27 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1122,10 +1137,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/2026 Family League 2026 Betting Odds.xlsx
+++ b/data/odds/2026 Family League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="72">
   <si>
     <t>Record</t>
   </si>
@@ -30,13 +30,16 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Gabe's Great Team</t>
+  </si>
+  <si>
+    <t>For Me to Poop On</t>
+  </si>
+  <si>
     <t>Noah's Nifty Team</t>
   </si>
   <si>
-    <t>For Me to Poop On</t>
-  </si>
-  <si>
-    <t>Gabe's Great Team</t>
+    <t>Jackson's Scary Team</t>
   </si>
   <si>
     <t>That movie was great...</t>
@@ -45,178 +48,190 @@
     <t>Your Mom</t>
   </si>
   <si>
-    <t>Jackson's Scary Team</t>
+    <t>Big Bosh Bashers</t>
+  </si>
+  <si>
+    <t>lawrence's Lucrative Team</t>
+  </si>
+  <si>
+    <t>ICSquirrels</t>
   </si>
   <si>
     <t>Ragebaiters</t>
   </si>
   <si>
-    <t>Big Bosh Bashers</t>
-  </si>
-  <si>
-    <t>lawrence's Lucrative Team</t>
+    <t>Flacillionares</t>
   </si>
   <si>
     <t>Delco Dee</t>
   </si>
   <si>
-    <t>ICSquirrels</t>
-  </si>
-  <si>
-    <t>Flacillionares</t>
-  </si>
-  <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>0-4</t>
-  </si>
-  <si>
-    <t>1-3</t>
+    <t>5-0</t>
+  </si>
+  <si>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>0-5</t>
+  </si>
+  <si>
+    <t>1-4</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>97.9%</t>
-  </si>
-  <si>
-    <t>94.3%</t>
-  </si>
-  <si>
-    <t>73.3%</t>
-  </si>
-  <si>
-    <t>67.1%</t>
-  </si>
-  <si>
-    <t>25.1%</t>
-  </si>
-  <si>
-    <t>22.3%</t>
-  </si>
-  <si>
-    <t>13.3%</t>
-  </si>
-  <si>
-    <t>5.0%</t>
-  </si>
-  <si>
-    <t>1.7%</t>
+    <t>99.8%</t>
+  </si>
+  <si>
+    <t>90.6%</t>
+  </si>
+  <si>
+    <t>86.4%</t>
+  </si>
+  <si>
+    <t>66.0%</t>
+  </si>
+  <si>
+    <t>16.9%</t>
+  </si>
+  <si>
+    <t>13.6%</t>
+  </si>
+  <si>
+    <t>12.5%</t>
+  </si>
+  <si>
+    <t>8.9%</t>
+  </si>
+  <si>
+    <t>4.0%</t>
+  </si>
+  <si>
+    <t>1.3%</t>
+  </si>
+  <si>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-49900</t>
+  </si>
+  <si>
+    <t>-964</t>
+  </si>
+  <si>
+    <t>-635</t>
+  </si>
+  <si>
+    <t>-194</t>
+  </si>
+  <si>
+    <t>+492</t>
+  </si>
+  <si>
+    <t>+635</t>
+  </si>
+  <si>
+    <t>+700</t>
+  </si>
+  <si>
+    <t>+1024</t>
+  </si>
+  <si>
+    <t>+2400</t>
+  </si>
+  <si>
+    <t>+7592</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>65.4%</t>
+  </si>
+  <si>
+    <t>20.3%</t>
+  </si>
+  <si>
+    <t>13.1%</t>
+  </si>
+  <si>
+    <t>0.8%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-99900</t>
-  </si>
-  <si>
-    <t>-4662</t>
-  </si>
-  <si>
-    <t>-1654</t>
-  </si>
-  <si>
-    <t>-275</t>
-  </si>
-  <si>
-    <t>-204</t>
-  </si>
-  <si>
-    <t>+298</t>
-  </si>
-  <si>
-    <t>+348</t>
-  </si>
-  <si>
-    <t>+652</t>
-  </si>
-  <si>
-    <t>+1900</t>
-  </si>
-  <si>
-    <t>+5782</t>
+    <t>-189</t>
+  </si>
+  <si>
+    <t>+393</t>
+  </si>
+  <si>
+    <t>+663</t>
+  </si>
+  <si>
+    <t>+12400</t>
+  </si>
+  <si>
+    <t>+33233</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>49.4%</t>
-  </si>
-  <si>
-    <t>40.0%</t>
-  </si>
-  <si>
-    <t>6.4%</t>
-  </si>
-  <si>
-    <t>3.6%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>+102</t>
-  </si>
-  <si>
-    <t>+150</t>
-  </si>
-  <si>
-    <t>+1462</t>
-  </si>
-  <si>
-    <t>+2678</t>
-  </si>
-  <si>
-    <t>+19900</t>
-  </si>
-  <si>
-    <t>68.5%</t>
-  </si>
-  <si>
-    <t>19.9%</t>
-  </si>
-  <si>
-    <t>6.8%</t>
-  </si>
-  <si>
-    <t>1.8%</t>
-  </si>
-  <si>
-    <t>1.5%</t>
-  </si>
-  <si>
-    <t>1.4%</t>
-  </si>
-  <si>
-    <t>-217</t>
-  </si>
-  <si>
-    <t>+403</t>
-  </si>
-  <si>
-    <t>+1371</t>
-  </si>
-  <si>
-    <t>+5456</t>
-  </si>
-  <si>
-    <t>+6567</t>
-  </si>
-  <si>
-    <t>+7043</t>
+    <t>51.8%</t>
+  </si>
+  <si>
+    <t>23.8%</t>
+  </si>
+  <si>
+    <t>10.2%</t>
+  </si>
+  <si>
+    <t>5.8%</t>
+  </si>
+  <si>
+    <t>5.5%</t>
+  </si>
+  <si>
+    <t>2.7%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>-107</t>
+  </si>
+  <si>
+    <t>+320</t>
+  </si>
+  <si>
+    <t>+880</t>
+  </si>
+  <si>
+    <t>+1624</t>
+  </si>
+  <si>
+    <t>+1718</t>
+  </si>
+  <si>
+    <t>+3604</t>
+  </si>
+  <si>
+    <t>+49900</t>
   </si>
 </sst>
 </file>
@@ -599,10 +614,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -613,10 +628,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -624,13 +639,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -638,13 +653,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -652,13 +667,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -666,13 +681,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -683,10 +698,10 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -697,10 +712,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -708,13 +723,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -722,13 +737,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -736,13 +751,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -750,13 +765,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -777,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -785,30 +800,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -816,41 +831,41 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -858,97 +873,97 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -969,7 +984,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -980,13 +995,13 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -994,13 +1009,13 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1008,97 +1023,97 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1109,38 +1124,38 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/2026 Family League 2026 Betting Odds.xlsx
+++ b/data/odds/2026 Family League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="69">
   <si>
     <t>Record</t>
   </si>
@@ -30,15 +30,15 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Noah's Nifty Team</t>
+  </si>
+  <si>
+    <t>For Me to Poop On</t>
+  </si>
+  <si>
     <t>Gabe's Great Team</t>
   </si>
   <si>
-    <t>For Me to Poop On</t>
-  </si>
-  <si>
-    <t>Noah's Nifty Team</t>
-  </si>
-  <si>
     <t>Jackson's Scary Team</t>
   </si>
   <si>
@@ -48,190 +48,181 @@
     <t>Your Mom</t>
   </si>
   <si>
+    <t>lawrence's Lucrative Team</t>
+  </si>
+  <si>
+    <t>Ragebaiters</t>
+  </si>
+  <si>
     <t>Big Bosh Bashers</t>
   </si>
   <si>
-    <t>lawrence's Lucrative Team</t>
-  </si>
-  <si>
     <t>ICSquirrels</t>
   </si>
   <si>
-    <t>Ragebaiters</t>
-  </si>
-  <si>
     <t>Flacillionares</t>
   </si>
   <si>
     <t>Delco Dee</t>
   </si>
   <si>
-    <t>5-0</t>
-  </si>
-  <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>0-5</t>
-  </si>
-  <si>
-    <t>1-4</t>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>6-0</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>0-6</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>99.8%</t>
-  </si>
-  <si>
-    <t>90.6%</t>
-  </si>
-  <si>
-    <t>86.4%</t>
-  </si>
-  <si>
-    <t>66.0%</t>
-  </si>
-  <si>
-    <t>16.9%</t>
-  </si>
-  <si>
-    <t>13.6%</t>
-  </si>
-  <si>
-    <t>12.5%</t>
-  </si>
-  <si>
-    <t>8.9%</t>
-  </si>
-  <si>
-    <t>4.0%</t>
-  </si>
-  <si>
-    <t>1.3%</t>
+    <t>99.9%</t>
+  </si>
+  <si>
+    <t>99.5%</t>
+  </si>
+  <si>
+    <t>96.4%</t>
+  </si>
+  <si>
+    <t>96.0%</t>
+  </si>
+  <si>
+    <t>35.6%</t>
+  </si>
+  <si>
+    <t>35.0%</t>
+  </si>
+  <si>
+    <t>16.5%</t>
+  </si>
+  <si>
+    <t>13.9%</t>
+  </si>
+  <si>
+    <t>4.2%</t>
+  </si>
+  <si>
+    <t>2.9%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-49900</t>
-  </si>
-  <si>
-    <t>-964</t>
-  </si>
-  <si>
-    <t>-635</t>
-  </si>
-  <si>
-    <t>-194</t>
-  </si>
-  <si>
-    <t>+492</t>
-  </si>
-  <si>
-    <t>+635</t>
-  </si>
-  <si>
-    <t>+700</t>
-  </si>
-  <si>
-    <t>+1024</t>
-  </si>
-  <si>
-    <t>+2400</t>
-  </si>
-  <si>
-    <t>+7592</t>
+    <t>-19900</t>
+  </si>
+  <si>
+    <t>-2678</t>
+  </si>
+  <si>
+    <t>-2400</t>
+  </si>
+  <si>
+    <t>+181</t>
+  </si>
+  <si>
+    <t>+186</t>
+  </si>
+  <si>
+    <t>+506</t>
+  </si>
+  <si>
+    <t>+619</t>
+  </si>
+  <si>
+    <t>+2281</t>
+  </si>
+  <si>
+    <t>+3348</t>
+  </si>
+  <si>
+    <t>+99900</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>65.4%</t>
-  </si>
-  <si>
-    <t>20.3%</t>
-  </si>
-  <si>
-    <t>13.1%</t>
-  </si>
-  <si>
-    <t>0.8%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
+    <t>48.2%</t>
+  </si>
+  <si>
+    <t>27.5%</t>
+  </si>
+  <si>
+    <t>18.9%</t>
+  </si>
+  <si>
+    <t>3.3%</t>
+  </si>
+  <si>
+    <t>2.1%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-189</t>
-  </si>
-  <si>
-    <t>+393</t>
-  </si>
-  <si>
-    <t>+663</t>
-  </si>
-  <si>
-    <t>+12400</t>
-  </si>
-  <si>
-    <t>+33233</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>51.8%</t>
-  </si>
-  <si>
-    <t>23.8%</t>
-  </si>
-  <si>
-    <t>10.2%</t>
-  </si>
-  <si>
-    <t>5.8%</t>
-  </si>
-  <si>
-    <t>5.5%</t>
-  </si>
-  <si>
-    <t>2.7%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>-107</t>
-  </si>
-  <si>
-    <t>+320</t>
-  </si>
-  <si>
-    <t>+880</t>
-  </si>
-  <si>
-    <t>+1624</t>
-  </si>
-  <si>
-    <t>+1718</t>
-  </si>
-  <si>
-    <t>+3604</t>
-  </si>
-  <si>
-    <t>+49900</t>
+    <t>+107</t>
+  </si>
+  <si>
+    <t>+264</t>
+  </si>
+  <si>
+    <t>+429</t>
+  </si>
+  <si>
+    <t>+2930</t>
+  </si>
+  <si>
+    <t>+4662</t>
+  </si>
+  <si>
+    <t>69.8%</t>
+  </si>
+  <si>
+    <t>17.6%</t>
+  </si>
+  <si>
+    <t>7.5%</t>
+  </si>
+  <si>
+    <t>2.4%</t>
+  </si>
+  <si>
+    <t>1.9%</t>
+  </si>
+  <si>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>-231</t>
+  </si>
+  <si>
+    <t>+468</t>
+  </si>
+  <si>
+    <t>+1233</t>
+  </si>
+  <si>
+    <t>+4067</t>
+  </si>
+  <si>
+    <t>+5163</t>
+  </si>
+  <si>
+    <t>+14186</t>
   </si>
 </sst>
 </file>
@@ -617,7 +608,7 @@
         <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -628,10 +619,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -639,13 +630,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -653,13 +644,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -667,13 +658,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -684,10 +675,10 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -695,13 +686,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -709,13 +700,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -726,10 +717,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -737,13 +728,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -751,13 +742,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -765,13 +756,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -792,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -800,13 +791,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
         <v>52</v>
@@ -814,13 +805,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
         <v>53</v>
@@ -831,10 +822,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
         <v>54</v>
@@ -845,10 +836,10 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
         <v>55</v>
@@ -859,10 +850,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -870,44 +861,44 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
         <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -921,35 +912,35 @@
         <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
         <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
         <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -957,13 +948,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
         <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -984,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -995,13 +986,13 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1009,13 +1000,13 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1023,27 +1014,27 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1054,66 +1045,66 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
         <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
         <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1127,7 +1118,7 @@
         <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1135,13 +1126,13 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
         <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1149,13 +1140,13 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
         <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/2026 Family League 2026 Betting Odds.xlsx
+++ b/data/odds/2026 Family League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="65">
   <si>
     <t>Record</t>
   </si>
@@ -45,18 +45,18 @@
     <t>That movie was great...</t>
   </si>
   <si>
+    <t>Big Bosh Bashers</t>
+  </si>
+  <si>
+    <t>lawrence's Lucrative Team</t>
+  </si>
+  <si>
+    <t>Ragebaiters</t>
+  </si>
+  <si>
     <t>Your Mom</t>
   </si>
   <si>
-    <t>lawrence's Lucrative Team</t>
-  </si>
-  <si>
-    <t>Ragebaiters</t>
-  </si>
-  <si>
-    <t>Big Bosh Bashers</t>
-  </si>
-  <si>
     <t>ICSquirrels</t>
   </si>
   <si>
@@ -66,88 +66,91 @@
     <t>Delco Dee</t>
   </si>
   <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>6-0</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>0-6</t>
-  </si>
-  <si>
-    <t>100.0%</t>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>7-0</t>
+  </si>
+  <si>
+    <t>6-1</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>1-6</t>
+  </si>
+  <si>
+    <t>0-7</t>
   </si>
   <si>
     <t>99.9%</t>
   </si>
   <si>
+    <t>99.8%</t>
+  </si>
+  <si>
     <t>99.5%</t>
   </si>
   <si>
-    <t>96.4%</t>
-  </si>
-  <si>
-    <t>96.0%</t>
-  </si>
-  <si>
-    <t>35.6%</t>
-  </si>
-  <si>
-    <t>35.0%</t>
-  </si>
-  <si>
-    <t>16.5%</t>
-  </si>
-  <si>
-    <t>13.9%</t>
-  </si>
-  <si>
-    <t>4.2%</t>
-  </si>
-  <si>
-    <t>2.9%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
+    <t>99.0%</t>
+  </si>
+  <si>
+    <t>28.6%</t>
+  </si>
+  <si>
+    <t>26.3%</t>
+  </si>
+  <si>
+    <t>26.1%</t>
+  </si>
+  <si>
+    <t>18.9%</t>
+  </si>
+  <si>
+    <t>1.3%</t>
+  </si>
+  <si>
+    <t>1.1%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
+    <t>-49900</t>
+  </si>
+  <si>
     <t>-19900</t>
   </si>
   <si>
-    <t>-2678</t>
-  </si>
-  <si>
-    <t>-2400</t>
-  </si>
-  <si>
-    <t>+181</t>
-  </si>
-  <si>
-    <t>+186</t>
-  </si>
-  <si>
-    <t>+506</t>
-  </si>
-  <si>
-    <t>+619</t>
-  </si>
-  <si>
-    <t>+2281</t>
-  </si>
-  <si>
-    <t>+3348</t>
+    <t>-9900</t>
+  </si>
+  <si>
+    <t>+250</t>
+  </si>
+  <si>
+    <t>+280</t>
+  </si>
+  <si>
+    <t>+283</t>
+  </si>
+  <si>
+    <t>+429</t>
+  </si>
+  <si>
+    <t>+7592</t>
+  </si>
+  <si>
+    <t>+8991</t>
   </si>
   <si>
     <t>+99900</t>
@@ -156,73 +159,58 @@
     <t>Probability</t>
   </si>
   <si>
-    <t>48.2%</t>
-  </si>
-  <si>
-    <t>27.5%</t>
-  </si>
-  <si>
-    <t>18.9%</t>
-  </si>
-  <si>
-    <t>3.3%</t>
-  </si>
-  <si>
-    <t>2.1%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>+107</t>
-  </si>
-  <si>
-    <t>+264</t>
-  </si>
-  <si>
-    <t>+429</t>
-  </si>
-  <si>
-    <t>+2930</t>
-  </si>
-  <si>
-    <t>+4662</t>
-  </si>
-  <si>
-    <t>69.8%</t>
-  </si>
-  <si>
-    <t>17.6%</t>
-  </si>
-  <si>
-    <t>7.5%</t>
-  </si>
-  <si>
-    <t>2.4%</t>
-  </si>
-  <si>
-    <t>1.9%</t>
-  </si>
-  <si>
-    <t>0.7%</t>
-  </si>
-  <si>
-    <t>-231</t>
-  </si>
-  <si>
-    <t>+468</t>
-  </si>
-  <si>
-    <t>+1233</t>
-  </si>
-  <si>
-    <t>+4067</t>
-  </si>
-  <si>
-    <t>+5163</t>
-  </si>
-  <si>
-    <t>+14186</t>
+    <t>32.4%</t>
+  </si>
+  <si>
+    <t>26.8%</t>
+  </si>
+  <si>
+    <t>17.9%</t>
+  </si>
+  <si>
+    <t>15.8%</t>
+  </si>
+  <si>
+    <t>7.1%</t>
+  </si>
+  <si>
+    <t>+209</t>
+  </si>
+  <si>
+    <t>+273</t>
+  </si>
+  <si>
+    <t>+459</t>
+  </si>
+  <si>
+    <t>+533</t>
+  </si>
+  <si>
+    <t>+1308</t>
+  </si>
+  <si>
+    <t>70.3%</t>
+  </si>
+  <si>
+    <t>16.7%</t>
+  </si>
+  <si>
+    <t>11.7%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>-237</t>
+  </si>
+  <si>
+    <t>+499</t>
+  </si>
+  <si>
+    <t>+755</t>
+  </si>
+  <si>
+    <t>+49900</t>
   </si>
 </sst>
 </file>
@@ -605,10 +593,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -616,13 +604,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -630,13 +618,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -644,13 +632,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -658,13 +646,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -675,10 +663,10 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -686,13 +674,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -700,13 +688,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -714,13 +702,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -728,13 +716,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -742,13 +730,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -756,13 +744,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -783,7 +771,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -791,13 +779,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
         <v>52</v>
@@ -805,13 +793,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
         <v>53</v>
@@ -822,10 +810,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
         <v>54</v>
@@ -836,10 +824,10 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
         <v>55</v>
@@ -850,10 +838,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
         <v>56</v>
@@ -864,13 +852,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -878,13 +866,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -892,27 +880,27 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -920,27 +908,27 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -948,13 +936,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -975,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -986,83 +974,83 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
         <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
         <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
         <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1070,41 +1058,41 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1112,13 +1100,13 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1126,13 +1114,13 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1140,13 +1128,13 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/2026 Family League 2026 Betting Odds.xlsx
+++ b/data/odds/2026 Family League 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="68">
   <si>
     <t>Record</t>
   </si>
@@ -90,124 +90,133 @@
     <t>0-7</t>
   </si>
   <si>
-    <t>99.9%</t>
-  </si>
-  <si>
     <t>99.8%</t>
   </si>
   <si>
+    <t>99.7%</t>
+  </si>
+  <si>
     <t>99.5%</t>
   </si>
   <si>
-    <t>99.0%</t>
-  </si>
-  <si>
-    <t>28.6%</t>
-  </si>
-  <si>
-    <t>26.3%</t>
-  </si>
-  <si>
-    <t>26.1%</t>
-  </si>
-  <si>
-    <t>18.9%</t>
-  </si>
-  <si>
-    <t>1.3%</t>
+    <t>99.4%</t>
+  </si>
+  <si>
+    <t>99.3%</t>
+  </si>
+  <si>
+    <t>28.8%</t>
+  </si>
+  <si>
+    <t>27.5%</t>
+  </si>
+  <si>
+    <t>24.8%</t>
+  </si>
+  <si>
+    <t>19.9%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>-49900</t>
+  </si>
+  <si>
+    <t>-33233</t>
+  </si>
+  <si>
+    <t>-19900</t>
+  </si>
+  <si>
+    <t>-16567</t>
+  </si>
+  <si>
+    <t>-14186</t>
+  </si>
+  <si>
+    <t>+247</t>
+  </si>
+  <si>
+    <t>+264</t>
+  </si>
+  <si>
+    <t>+303</t>
+  </si>
+  <si>
+    <t>+403</t>
+  </si>
+  <si>
+    <t>+16567</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>30.8%</t>
+  </si>
+  <si>
+    <t>26.6%</t>
+  </si>
+  <si>
+    <t>20.3%</t>
+  </si>
+  <si>
+    <t>14.1%</t>
+  </si>
+  <si>
+    <t>8.2%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>+225</t>
+  </si>
+  <si>
+    <t>+276</t>
+  </si>
+  <si>
+    <t>+393</t>
+  </si>
+  <si>
+    <t>+609</t>
+  </si>
+  <si>
+    <t>+1120</t>
+  </si>
+  <si>
+    <t>66.5%</t>
+  </si>
+  <si>
+    <t>19.4%</t>
+  </si>
+  <si>
+    <t>12.7%</t>
   </si>
   <si>
     <t>1.1%</t>
   </si>
   <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-99900</t>
-  </si>
-  <si>
-    <t>-49900</t>
-  </si>
-  <si>
-    <t>-19900</t>
-  </si>
-  <si>
-    <t>-9900</t>
-  </si>
-  <si>
-    <t>+250</t>
-  </si>
-  <si>
-    <t>+280</t>
-  </si>
-  <si>
-    <t>+283</t>
-  </si>
-  <si>
-    <t>+429</t>
-  </si>
-  <si>
-    <t>+7592</t>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>-199</t>
+  </si>
+  <si>
+    <t>+415</t>
+  </si>
+  <si>
+    <t>+687</t>
   </si>
   <si>
     <t>+8991</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>32.4%</t>
-  </si>
-  <si>
-    <t>26.8%</t>
-  </si>
-  <si>
-    <t>17.9%</t>
-  </si>
-  <si>
-    <t>15.8%</t>
-  </si>
-  <si>
-    <t>7.1%</t>
-  </si>
-  <si>
-    <t>+209</t>
-  </si>
-  <si>
-    <t>+273</t>
-  </si>
-  <si>
-    <t>+459</t>
-  </si>
-  <si>
-    <t>+533</t>
-  </si>
-  <si>
-    <t>+1308</t>
-  </si>
-  <si>
-    <t>70.3%</t>
-  </si>
-  <si>
-    <t>16.7%</t>
-  </si>
-  <si>
-    <t>11.7%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>-237</t>
-  </si>
-  <si>
-    <t>+499</t>
-  </si>
-  <si>
-    <t>+755</t>
   </si>
   <si>
     <t>+49900</t>
@@ -635,10 +644,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -649,10 +658,10 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -663,10 +672,10 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -677,10 +686,10 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -691,10 +700,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -705,10 +714,10 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -719,10 +728,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -788,7 +797,7 @@
         <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -802,7 +811,7 @@
         <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -816,7 +825,7 @@
         <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -830,7 +839,7 @@
         <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -844,7 +853,7 @@
         <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -855,7 +864,7 @@
         <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
         <v>45</v>
@@ -869,7 +878,7 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
         <v>45</v>
@@ -883,7 +892,7 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
         <v>45</v>
@@ -897,7 +906,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
         <v>45</v>
@@ -911,7 +920,7 @@
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
         <v>45</v>
@@ -925,7 +934,7 @@
         <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
         <v>45</v>
@@ -939,7 +948,7 @@
         <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
         <v>45</v>
@@ -977,10 +986,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -991,10 +1000,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1005,10 +1014,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1019,32 +1028,32 @@
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
         <v>34</v>
@@ -1055,13 +1064,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
         <v>45</v>
@@ -1069,13 +1078,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
         <v>45</v>
@@ -1083,13 +1092,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
         <v>45</v>
@@ -1103,7 +1112,7 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
         <v>45</v>
@@ -1117,7 +1126,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
         <v>45</v>
@@ -1131,7 +1140,7 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
         <v>45</v>
